--- a/Pick Faces_Output.xlsx
+++ b/Pick Faces_Output.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top_pairs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PickFace" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pick Faces" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1502,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1523,22 +1523,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Cartons per day (90 Percentile)</t>
+          <t>ABC Class</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>XYZ Class</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cartons per day (Tiered)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Pallets per day at 90%</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Pick Faces (pallets)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ABC Class</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>XYZ Class</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cartons at Pick Faces</t>
         </is>
       </c>
     </row>
@@ -1554,21 +1564,27 @@
       <c r="C2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
-        <v>700.5000000000009</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1322.01</v>
+      </c>
+      <c r="G2" t="n">
+        <v>21</v>
+      </c>
+      <c r="H2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I2" t="n">
+        <v>1408</v>
       </c>
     </row>
     <row r="3">
@@ -1583,21 +1599,27 @@
       <c r="C3" t="n">
         <v>60</v>
       </c>
-      <c r="D3" t="n">
-        <v>347.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>733.2399999999981</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="4">
@@ -1612,21 +1634,27 @@
       <c r="C4" t="n">
         <v>60</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -1641,21 +1669,27 @@
       <c r="C5" t="n">
         <v>20</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>24</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -1670,21 +1704,27 @@
       <c r="C6" t="n">
         <v>60</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>22.6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -1699,21 +1739,27 @@
       <c r="C7" t="n">
         <v>72</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>91.59999999999999</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -1728,21 +1774,27 @@
       <c r="C8" t="n">
         <v>40</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>106.5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="9">
@@ -1757,21 +1809,27 @@
       <c r="C9" t="n">
         <v>60</v>
       </c>
-      <c r="D9" t="n">
-        <v>125</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>217.6399999999999</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -1786,21 +1844,27 @@
       <c r="C10" t="n">
         <v>60</v>
       </c>
-      <c r="D10" t="n">
-        <v>1026</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1784.999999999997</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="11">
@@ -1815,21 +1879,27 @@
       <c r="C11" t="n">
         <v>32</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>50</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -1844,21 +1914,27 @@
       <c r="C12" t="n">
         <v>120</v>
       </c>
-      <c r="D12" t="n">
-        <v>339.6000000000001</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>676.1000000000003</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I12" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="13">
@@ -1873,21 +1949,27 @@
       <c r="C13" t="n">
         <v>60</v>
       </c>
-      <c r="D13" t="n">
-        <v>132.2</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>256.6800000000009</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
         <v>3</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I13" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="14">
@@ -1902,21 +1984,27 @@
       <c r="C14" t="n">
         <v>48</v>
       </c>
-      <c r="D14" t="n">
-        <v>274</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>560.9999999999986</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
         <v>6</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I14" t="n">
+        <v>576</v>
       </c>
     </row>
     <row r="15">
@@ -1931,21 +2019,27 @@
       <c r="C15" t="n">
         <v>60</v>
       </c>
-      <c r="D15" t="n">
-        <v>73</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>140.5799999999995</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I15" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="16">
@@ -1960,21 +2054,27 @@
       <c r="C16" t="n">
         <v>72</v>
       </c>
-      <c r="D16" t="n">
-        <v>291.8000000000001</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>582.16</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I16" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="17">
@@ -1989,21 +2089,27 @@
       <c r="C17" t="n">
         <v>60</v>
       </c>
-      <c r="D17" t="n">
-        <v>279</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>508.0000000000009</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H17" t="n">
         <v>5</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I17" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -2018,21 +2124,27 @@
       <c r="C18" t="n">
         <v>64</v>
       </c>
-      <c r="D18" t="n">
-        <v>308</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>651.0000000000009</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>768</v>
       </c>
     </row>
     <row r="19">
@@ -2047,21 +2159,27 @@
       <c r="C19" t="n">
         <v>36</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>109.6</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>4</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="20">
@@ -2076,21 +2194,27 @@
       <c r="C20" t="n">
         <v>48</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>279.9</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="21">
@@ -2105,21 +2229,27 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>123</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>7</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="22">
@@ -2134,21 +2264,27 @@
       <c r="C22" t="n">
         <v>72</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>165.6000000000001</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="23">
@@ -2163,21 +2299,27 @@
       <c r="C23" t="n">
         <v>72</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>418.9</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>6</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H23" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="24">
@@ -2192,21 +2334,27 @@
       <c r="C24" t="n">
         <v>36</v>
       </c>
-      <c r="D24" t="n">
-        <v>399</v>
-      </c>
-      <c r="E24" t="n">
-        <v>12</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>735.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>21</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" t="n">
+        <v>792</v>
       </c>
     </row>
     <row r="25">
@@ -2221,21 +2369,27 @@
       <c r="C25" t="n">
         <v>40</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>252</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>7</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="26">
@@ -2250,21 +2404,27 @@
       <c r="C26" t="n">
         <v>60</v>
       </c>
-      <c r="D26" t="n">
-        <v>1040.7</v>
-      </c>
-      <c r="E26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1673.730000000001</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28</v>
+      </c>
+      <c r="H26" t="n">
+        <v>14</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1680</v>
       </c>
     </row>
     <row r="27">
@@ -2279,21 +2439,27 @@
       <c r="C27" t="n">
         <v>50</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>117.2000000000001</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="28">
@@ -2308,21 +2474,27 @@
       <c r="C28" t="n">
         <v>30</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>46.79999999999999</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>2</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="29">
@@ -2337,21 +2509,27 @@
       <c r="C29" t="n">
         <v>32</v>
       </c>
-      <c r="D29" t="n">
-        <v>108</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>192.2499999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I29" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="30">
@@ -2366,21 +2544,27 @@
       <c r="C30" t="n">
         <v>60</v>
       </c>
-      <c r="D30" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>236.2299999999993</v>
+      </c>
+      <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I30" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -2395,21 +2579,27 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>89</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>170.5700000000002</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
         <v>3</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I31" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="32">
@@ -2424,21 +2614,27 @@
       <c r="C32" t="n">
         <v>140</v>
       </c>
-      <c r="D32" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I32" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="33">
@@ -2453,21 +2649,27 @@
       <c r="C33" t="n">
         <v>140</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>471.2</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>4</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>560</v>
       </c>
     </row>
     <row r="34">
@@ -2482,21 +2684,27 @@
       <c r="C34" t="n">
         <v>20</v>
       </c>
-      <c r="D34" t="n">
-        <v>135</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>264.7199999999998</v>
+      </c>
+      <c r="G34" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" t="n">
         <v>7</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I34" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="35">
@@ -2511,21 +2719,27 @@
       <c r="C35" t="n">
         <v>20</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>87.59999999999998</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>5</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="36">
@@ -2540,21 +2754,27 @@
       <c r="C36" t="n">
         <v>48</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>1.674994</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>1</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="37">
@@ -2569,21 +2789,27 @@
       <c r="C37" t="n">
         <v>48</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>102.6</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="38">
@@ -2598,21 +2824,27 @@
       <c r="C38" t="n">
         <v>48</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>77.19999999999999</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="39">
@@ -2627,21 +2859,27 @@
       <c r="C39" t="n">
         <v>20</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>32</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>2</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2656,21 +2894,27 @@
       <c r="C40" t="n">
         <v>72</v>
       </c>
-      <c r="D40" t="n">
-        <v>84</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>196.2799999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I40" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="41">
@@ -2685,21 +2929,27 @@
       <c r="C41" t="n">
         <v>48</v>
       </c>
-      <c r="D41" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>247.29</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="42">
@@ -2714,21 +2964,27 @@
       <c r="C42" t="n">
         <v>20</v>
       </c>
-      <c r="D42" t="n">
-        <v>65.60000000000002</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="43">
@@ -2743,21 +2999,27 @@
       <c r="C43" t="n">
         <v>20</v>
       </c>
-      <c r="D43" t="n">
-        <v>73.66666800000002</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>127.5199999999998</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I43" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="44">
@@ -2772,21 +3034,27 @@
       <c r="C44" t="n">
         <v>72</v>
       </c>
-      <c r="D44" t="n">
-        <v>94.30000000000001</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>172.24</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
         <v>2</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I44" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="45">
@@ -2801,21 +3069,27 @@
       <c r="C45" t="n">
         <v>72</v>
       </c>
-      <c r="D45" t="n">
-        <v>92.80000000000007</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="G45" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" t="n">
         <v>2</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I45" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="46">
@@ -2830,21 +3104,27 @@
       <c r="C46" t="n">
         <v>36</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
         <v>53.50000000000001</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>2</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -2859,21 +3139,27 @@
       <c r="C47" t="n">
         <v>32</v>
       </c>
-      <c r="D47" t="n">
-        <v>303.0000000000002</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>605.7700000000025</v>
+      </c>
+      <c r="G47" t="n">
+        <v>19</v>
+      </c>
+      <c r="H47" t="n">
         <v>10</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I47" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="48">
@@ -2888,21 +3174,27 @@
       <c r="C48" t="n">
         <v>120</v>
       </c>
-      <c r="D48" t="n">
-        <v>899.1</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1703.660000000001</v>
+      </c>
+      <c r="G48" t="n">
+        <v>15</v>
+      </c>
+      <c r="H48" t="n">
         <v>8</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I48" t="n">
+        <v>1920</v>
       </c>
     </row>
     <row r="49">
@@ -2917,21 +3209,27 @@
       <c r="C49" t="n">
         <v>64</v>
       </c>
-      <c r="D49" t="n">
-        <v>253.8000000000001</v>
-      </c>
-      <c r="E49" t="n">
-        <v>4</v>
-      </c>
-      <c r="F49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>583.7500000000009</v>
+      </c>
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
+      <c r="H49" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="50">
@@ -2946,21 +3244,27 @@
       <c r="C50" t="n">
         <v>60</v>
       </c>
-      <c r="D50" t="n">
-        <v>360</v>
-      </c>
-      <c r="E50" t="n">
-        <v>6</v>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>742.9999999999998</v>
+      </c>
+      <c r="G50" t="n">
+        <v>13</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7</v>
+      </c>
+      <c r="I50" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="51">
@@ -2975,21 +3279,27 @@
       <c r="C51" t="n">
         <v>20</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>227.0000000000001</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>12</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="52">
@@ -3004,21 +3314,27 @@
       <c r="C52" t="n">
         <v>30</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
         <v>48</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>2</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -3033,21 +3349,27 @@
       <c r="C53" t="n">
         <v>40</v>
       </c>
-      <c r="D53" t="n">
-        <v>216.2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>382.5600000000004</v>
+      </c>
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
+      <c r="H53" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="54">
@@ -3062,21 +3384,27 @@
       <c r="C54" t="n">
         <v>63</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
         <v>491.4000000000001</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>8</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H54" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>504</v>
       </c>
     </row>
     <row r="55">
@@ -3091,21 +3419,27 @@
       <c r="C55" t="n">
         <v>63</v>
       </c>
-      <c r="D55" t="n">
-        <v>1018.1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>17</v>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1918.010000000002</v>
+      </c>
+      <c r="G55" t="n">
+        <v>31</v>
+      </c>
+      <c r="H55" t="n">
+        <v>16</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="56">
@@ -3120,21 +3454,27 @@
       <c r="C56" t="n">
         <v>60</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
         <v>86.40000000000001</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>2</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="57">
@@ -3149,21 +3489,27 @@
       <c r="C57" t="n">
         <v>63</v>
       </c>
-      <c r="D57" t="n">
-        <v>516.2</v>
-      </c>
-      <c r="E57" t="n">
-        <v>9</v>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>784.4600000000002</v>
+      </c>
+      <c r="G57" t="n">
+        <v>13</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>882</v>
       </c>
     </row>
     <row r="58">
@@ -3178,21 +3524,27 @@
       <c r="C58" t="n">
         <v>64</v>
       </c>
-      <c r="D58" t="n">
-        <v>883</v>
-      </c>
-      <c r="E58" t="n">
-        <v>14</v>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1543.199999999997</v>
+      </c>
+      <c r="G58" t="n">
+        <v>25</v>
+      </c>
+      <c r="H58" t="n">
+        <v>13</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1664</v>
       </c>
     </row>
     <row r="59">
@@ -3207,21 +3559,27 @@
       <c r="C59" t="n">
         <v>60</v>
       </c>
-      <c r="D59" t="n">
-        <v>354.4</v>
-      </c>
-      <c r="E59" t="n">
-        <v>6</v>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>741.9600000000006</v>
+      </c>
+      <c r="G59" t="n">
+        <v>13</v>
+      </c>
+      <c r="H59" t="n">
+        <v>7</v>
+      </c>
+      <c r="I59" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="60">
@@ -3236,21 +3594,27 @@
       <c r="C60" t="n">
         <v>48</v>
       </c>
-      <c r="D60" t="n">
-        <v>133</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>205.2399999999998</v>
+      </c>
+      <c r="G60" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" t="n">
         <v>3</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I60" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="61">
@@ -3265,21 +3629,27 @@
       <c r="C61" t="n">
         <v>60</v>
       </c>
-      <c r="D61" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>295.0900000000004</v>
+      </c>
+      <c r="G61" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" t="n">
         <v>3</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I61" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="62">
@@ -3294,21 +3664,27 @@
       <c r="C62" t="n">
         <v>20</v>
       </c>
-      <c r="D62" t="n">
-        <v>88.30000000000001</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>133.6499999999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>7</v>
+      </c>
+      <c r="H62" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="63">
@@ -3323,21 +3699,27 @@
       <c r="C63" t="n">
         <v>20</v>
       </c>
-      <c r="D63" t="n">
-        <v>24.90000000000001</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="G63" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" t="n">
         <v>2</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I63" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="64">
@@ -3352,21 +3734,27 @@
       <c r="C64" t="n">
         <v>20</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>16</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
         <v>1</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -3381,21 +3769,27 @@
       <c r="C65" t="n">
         <v>30</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
         <v>40.8</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G65" t="n">
         <v>2</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="66">
@@ -3410,21 +3804,27 @@
       <c r="C66" t="n">
         <v>60</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
         <v>118.9</v>
       </c>
-      <c r="E66" t="n">
+      <c r="G66" t="n">
         <v>2</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="67">
@@ -3439,21 +3839,27 @@
       <c r="C67" t="n">
         <v>32</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v>154.1</v>
       </c>
-      <c r="E67" t="n">
+      <c r="G67" t="n">
         <v>5</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="68">
@@ -3468,21 +3874,27 @@
       <c r="C68" t="n">
         <v>20</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
         <v>91.5</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
         <v>5</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H68" t="n">
+        <v>3</v>
+      </c>
+      <c r="I68" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="69">
@@ -3497,21 +3909,27 @@
       <c r="C69" t="n">
         <v>48</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
         <v>139</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
         <v>3</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="70">
@@ -3526,21 +3944,27 @@
       <c r="C70" t="n">
         <v>50</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
         <v>206</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
         <v>5</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="71">
@@ -3555,21 +3979,27 @@
       <c r="C71" t="n">
         <v>42</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
         <v>121.0000000000001</v>
       </c>
-      <c r="E71" t="n">
+      <c r="G71" t="n">
         <v>3</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H71" t="n">
+        <v>2</v>
+      </c>
+      <c r="I71" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="72">
@@ -3584,21 +4014,27 @@
       <c r="C72" t="n">
         <v>60</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
         <v>250.7999999999997</v>
       </c>
-      <c r="E72" t="n">
+      <c r="G72" t="n">
         <v>5</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="73">
@@ -3613,21 +4049,27 @@
       <c r="C73" t="n">
         <v>20</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
         <v>56.7</v>
       </c>
-      <c r="E73" t="n">
+      <c r="G73" t="n">
         <v>3</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -3642,21 +4084,27 @@
       <c r="C74" t="n">
         <v>20</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v>78</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
         <v>4</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="75">
@@ -3671,21 +4119,27 @@
       <c r="C75" t="n">
         <v>42</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
         <v>129.8</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
         <v>4</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H75" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="76">
@@ -3700,21 +4154,27 @@
       <c r="C76" t="n">
         <v>20</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
         <v>359.2000000000002</v>
       </c>
-      <c r="E76" t="n">
+      <c r="G76" t="n">
         <v>18</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H76" t="n">
+        <v>9</v>
+      </c>
+      <c r="I76" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="77">
@@ -3729,21 +4189,27 @@
       <c r="C77" t="n">
         <v>42</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
         <v>376.6</v>
       </c>
-      <c r="E77" t="n">
+      <c r="G77" t="n">
         <v>9</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H77" t="n">
+        <v>5</v>
+      </c>
+      <c r="I77" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="78">
@@ -3758,21 +4224,27 @@
       <c r="C78" t="n">
         <v>42</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
         <v>202.8000000000001</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
         <v>5</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H78" t="n">
+        <v>3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>252</v>
       </c>
     </row>
     <row r="79">
@@ -3787,21 +4259,27 @@
       <c r="C79" t="n">
         <v>112</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
         <v>358.8</v>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
         <v>4</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H79" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="80">
@@ -3816,21 +4294,27 @@
       <c r="C80" t="n">
         <v>20</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
         <v>10</v>
       </c>
-      <c r="E80" t="n">
+      <c r="G80" t="n">
         <v>1</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -3845,21 +4329,27 @@
       <c r="C81" t="n">
         <v>72</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
         <v>1.8875</v>
       </c>
-      <c r="E81" t="n">
+      <c r="G81" t="n">
         <v>1</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="82">
@@ -3874,21 +4364,27 @@
       <c r="C82" t="n">
         <v>60</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
         <v>414</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
         <v>7</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H82" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="83">
@@ -3903,21 +4399,27 @@
       <c r="C83" t="n">
         <v>35</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
         <v>81.2</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
         <v>3</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H83" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="84">
@@ -3932,21 +4434,27 @@
       <c r="C84" t="n">
         <v>72</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
         <v>254.2000000000001</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
         <v>4</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="85">
@@ -3961,21 +4469,27 @@
       <c r="C85" t="n">
         <v>60</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
         <v>751</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
         <v>13</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H85" t="n">
+        <v>7</v>
+      </c>
+      <c r="I85" t="n">
+        <v>840</v>
       </c>
     </row>
     <row r="86">
@@ -3990,21 +4504,27 @@
       <c r="C86" t="n">
         <v>50</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
         <v>817.8000000000003</v>
       </c>
-      <c r="E86" t="n">
+      <c r="G86" t="n">
         <v>17</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H86" t="n">
+        <v>9</v>
+      </c>
+      <c r="I86" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="87">
@@ -4019,21 +4539,27 @@
       <c r="C87" t="n">
         <v>32</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
         <v>394.5</v>
       </c>
-      <c r="E87" t="n">
+      <c r="G87" t="n">
         <v>13</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="88">
@@ -4048,21 +4574,27 @@
       <c r="C88" t="n">
         <v>20</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
         <v>196</v>
       </c>
-      <c r="E88" t="n">
+      <c r="G88" t="n">
         <v>10</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H88" t="n">
+        <v>5</v>
+      </c>
+      <c r="I88" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="89">
@@ -4077,21 +4609,27 @@
       <c r="C89" t="n">
         <v>140</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
         <v>162.8</v>
       </c>
-      <c r="E89" t="n">
+      <c r="G89" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H89" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>280</v>
       </c>
     </row>
     <row r="90">
@@ -4106,21 +4644,27 @@
       <c r="C90" t="n">
         <v>36</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
         <v>367.7000000000001</v>
       </c>
-      <c r="E90" t="n">
+      <c r="G90" t="n">
         <v>11</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H90" t="n">
+        <v>6</v>
+      </c>
+      <c r="I90" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="91">
@@ -4135,21 +4679,27 @@
       <c r="C91" t="n">
         <v>50</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
         <v>570.5999999999998</v>
       </c>
-      <c r="E91" t="n">
+      <c r="G91" t="n">
         <v>12</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H91" t="n">
+        <v>6</v>
+      </c>
+      <c r="I91" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="92">
@@ -4164,21 +4714,27 @@
       <c r="C92" t="n">
         <v>72</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
         <v>223</v>
       </c>
-      <c r="E92" t="n">
+      <c r="G92" t="n">
         <v>4</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="93">
@@ -4193,21 +4749,27 @@
       <c r="C93" t="n">
         <v>160</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
         <v>187.2</v>
       </c>
-      <c r="E93" t="n">
+      <c r="G93" t="n">
         <v>2</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="94">
@@ -4222,21 +4784,27 @@
       <c r="C94" t="n">
         <v>30</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
         <v>104.4</v>
       </c>
-      <c r="E94" t="n">
+      <c r="G94" t="n">
         <v>4</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H94" t="n">
+        <v>2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="95">
@@ -4251,21 +4819,27 @@
       <c r="C95" t="n">
         <v>64</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
         <v>397.5000000000001</v>
       </c>
-      <c r="E95" t="n">
+      <c r="G95" t="n">
         <v>7</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H95" t="n">
+        <v>4</v>
+      </c>
+      <c r="I95" t="n">
+        <v>512</v>
       </c>
     </row>
     <row r="96">
@@ -4280,21 +4854,27 @@
       <c r="C96" t="n">
         <v>30</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
         <v>225</v>
       </c>
-      <c r="E96" t="n">
+      <c r="G96" t="n">
         <v>8</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="97">
@@ -4309,21 +4889,27 @@
       <c r="C97" t="n">
         <v>32</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
         <v>204.2</v>
       </c>
-      <c r="E97" t="n">
+      <c r="G97" t="n">
         <v>7</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H97" t="n">
+        <v>4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="98">
@@ -4338,21 +4924,27 @@
       <c r="C98" t="n">
         <v>20</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
         <v>148.0000000000001</v>
       </c>
-      <c r="E98" t="n">
+      <c r="G98" t="n">
         <v>8</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H98" t="n">
+        <v>4</v>
+      </c>
+      <c r="I98" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="99">
@@ -4367,21 +4959,27 @@
       <c r="C99" t="n">
         <v>72</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
         <v>336.6</v>
       </c>
-      <c r="E99" t="n">
+      <c r="G99" t="n">
         <v>5</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H99" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="100">
@@ -4396,21 +4994,27 @@
       <c r="C100" t="n">
         <v>64</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
         <v>346.8000000000001</v>
       </c>
-      <c r="E100" t="n">
+      <c r="G100" t="n">
         <v>6</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="101">
@@ -4425,21 +5029,27 @@
       <c r="C101" t="n">
         <v>20</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
         <v>40</v>
       </c>
-      <c r="E101" t="n">
+      <c r="G101" t="n">
         <v>2</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="102">
@@ -4454,21 +5064,27 @@
       <c r="C102" t="n">
         <v>48</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
         <v>68.19999999999999</v>
       </c>
-      <c r="E102" t="n">
+      <c r="G102" t="n">
         <v>2</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="103">
@@ -4483,21 +5099,27 @@
       <c r="C103" t="n">
         <v>40</v>
       </c>
-      <c r="D103" t="n">
-        <v>251.33334</v>
-      </c>
-      <c r="E103" t="n">
-        <v>7</v>
-      </c>
-      <c r="F103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>465.4000000000008</v>
+      </c>
+      <c r="G103" t="n">
+        <v>12</v>
+      </c>
+      <c r="H103" t="n">
+        <v>6</v>
+      </c>
+      <c r="I103" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="104">
@@ -4512,21 +5134,27 @@
       <c r="C104" t="n">
         <v>40</v>
       </c>
-      <c r="D104" t="n">
-        <v>64</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>143.68</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" t="n">
         <v>2</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I104" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="105">
@@ -4541,21 +5169,27 @@
       <c r="C105" t="n">
         <v>64</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
         <v>257.8000000000001</v>
       </c>
-      <c r="E105" t="n">
+      <c r="G105" t="n">
         <v>5</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="106">
@@ -4570,21 +5204,27 @@
       <c r="C106" t="n">
         <v>64</v>
       </c>
-      <c r="D106" t="n">
-        <v>197.3</v>
-      </c>
-      <c r="E106" t="n">
-        <v>4</v>
-      </c>
-      <c r="F106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>536.67</v>
+      </c>
+      <c r="G106" t="n">
+        <v>9</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="107">
@@ -4599,21 +5239,27 @@
       <c r="C107" t="n">
         <v>64</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
         <v>181.8</v>
       </c>
-      <c r="E107" t="n">
+      <c r="G107" t="n">
         <v>3</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H107" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="108">
@@ -4628,21 +5274,27 @@
       <c r="C108" t="n">
         <v>20</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
         <v>112.18</v>
       </c>
-      <c r="E108" t="n">
+      <c r="G108" t="n">
         <v>6</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H108" t="n">
+        <v>3</v>
+      </c>
+      <c r="I108" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="109">
@@ -4657,21 +5309,27 @@
       <c r="C109" t="n">
         <v>40</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
         <v>132</v>
       </c>
-      <c r="E109" t="n">
+      <c r="G109" t="n">
         <v>4</v>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="110">
@@ -4686,21 +5344,27 @@
       <c r="C110" t="n">
         <v>60</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
         <v>154</v>
       </c>
-      <c r="E110" t="n">
+      <c r="G110" t="n">
         <v>3</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="111">
@@ -4715,21 +5379,27 @@
       <c r="C111" t="n">
         <v>20</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
         <v>122.2</v>
       </c>
-      <c r="E111" t="n">
+      <c r="G111" t="n">
         <v>7</v>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H111" t="n">
+        <v>4</v>
+      </c>
+      <c r="I111" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="112">
@@ -4744,21 +5414,27 @@
       <c r="C112" t="n">
         <v>60</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
         <v>250.4000000000002</v>
       </c>
-      <c r="E112" t="n">
+      <c r="G112" t="n">
         <v>5</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H112" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="113">
@@ -4773,21 +5449,27 @@
       <c r="C113" t="n">
         <v>60</v>
       </c>
-      <c r="D113" t="n">
-        <v>542.4000000000002</v>
-      </c>
-      <c r="E113" t="n">
-        <v>10</v>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1041.900000000004</v>
+      </c>
+      <c r="G113" t="n">
+        <v>18</v>
+      </c>
+      <c r="H113" t="n">
+        <v>9</v>
+      </c>
+      <c r="I113" t="n">
+        <v>1080</v>
       </c>
     </row>
     <row r="114">
@@ -4802,21 +5484,27 @@
       <c r="C114" t="n">
         <v>60</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
         <v>311.2</v>
       </c>
-      <c r="E114" t="n">
+      <c r="G114" t="n">
         <v>6</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H114" t="n">
+        <v>3</v>
+      </c>
+      <c r="I114" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="115">
@@ -4831,21 +5519,27 @@
       <c r="C115" t="n">
         <v>20</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
         <v>140.3999999999999</v>
       </c>
-      <c r="E115" t="n">
+      <c r="G115" t="n">
         <v>8</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="116">
@@ -4860,21 +5554,27 @@
       <c r="C116" t="n">
         <v>64</v>
       </c>
-      <c r="D116" t="n">
-        <v>587.4000000000001</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1177.34</v>
+      </c>
+      <c r="G116" t="n">
+        <v>19</v>
+      </c>
+      <c r="H116" t="n">
         <v>10</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I116" t="n">
+        <v>1280</v>
       </c>
     </row>
     <row r="117">
@@ -4889,21 +5589,27 @@
       <c r="C117" t="n">
         <v>72</v>
       </c>
-      <c r="D117" t="n">
-        <v>214.4</v>
-      </c>
-      <c r="E117" t="n">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>374.1200000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>6</v>
+      </c>
+      <c r="H117" t="n">
         <v>3</v>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I117" t="n">
+        <v>432</v>
       </c>
     </row>
     <row r="118">
@@ -4918,21 +5624,27 @@
       <c r="C118" t="n">
         <v>60</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
         <v>129</v>
       </c>
-      <c r="E118" t="n">
+      <c r="G118" t="n">
         <v>3</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H118" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="119">
@@ -4947,21 +5659,27 @@
       <c r="C119" t="n">
         <v>25</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
         <v>161</v>
       </c>
-      <c r="E119" t="n">
+      <c r="G119" t="n">
         <v>7</v>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H119" t="n">
+        <v>4</v>
+      </c>
+      <c r="I119" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="120">
@@ -4976,21 +5694,27 @@
       <c r="C120" t="n">
         <v>30</v>
       </c>
-      <c r="D120" t="n">
-        <v>94.60000000000002</v>
-      </c>
-      <c r="E120" t="n">
-        <v>4</v>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>173.6400000000001</v>
+      </c>
+      <c r="G120" t="n">
+        <v>6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="121">
@@ -5005,21 +5729,27 @@
       <c r="C121" t="n">
         <v>32</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
         <v>1.9</v>
       </c>
-      <c r="E121" t="n">
+      <c r="G121" t="n">
         <v>1</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="122">
@@ -5034,21 +5764,27 @@
       <c r="C122" t="n">
         <v>65</v>
       </c>
-      <c r="D122" t="n">
-        <v>69</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>173.9999999999998</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="n">
         <v>2</v>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I122" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="123">
@@ -5063,21 +5799,27 @@
       <c r="C123" t="n">
         <v>60</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
         <v>146</v>
       </c>
-      <c r="E123" t="n">
+      <c r="G123" t="n">
         <v>3</v>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H123" t="n">
+        <v>2</v>
+      </c>
+      <c r="I123" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="124">
@@ -5092,21 +5834,27 @@
       <c r="C124" t="n">
         <v>60</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
         <v>165.9</v>
       </c>
-      <c r="E124" t="n">
+      <c r="G124" t="n">
         <v>3</v>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H124" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="125">
@@ -5121,21 +5869,27 @@
       <c r="C125" t="n">
         <v>60</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
         <v>209.2</v>
       </c>
-      <c r="E125" t="n">
+      <c r="G125" t="n">
         <v>4</v>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="126">
@@ -5150,21 +5904,27 @@
       <c r="C126" t="n">
         <v>48</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
         <v>182.8</v>
       </c>
-      <c r="E126" t="n">
+      <c r="G126" t="n">
         <v>4</v>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H126" t="n">
+        <v>2</v>
+      </c>
+      <c r="I126" t="n">
+        <v>192</v>
       </c>
     </row>
     <row r="127">
@@ -5179,21 +5939,27 @@
       <c r="C127" t="n">
         <v>48</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
         <v>219.2</v>
       </c>
-      <c r="E127" t="n">
+      <c r="G127" t="n">
         <v>5</v>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="128">
@@ -5208,21 +5974,27 @@
       <c r="C128" t="n">
         <v>48</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
         <v>210.2</v>
       </c>
-      <c r="E128" t="n">
+      <c r="G128" t="n">
         <v>5</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H128" t="n">
+        <v>3</v>
+      </c>
+      <c r="I128" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="129">
@@ -5237,21 +6009,27 @@
       <c r="C129" t="n">
         <v>40</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
         <v>238.4000000000002</v>
       </c>
-      <c r="E129" t="n">
+      <c r="G129" t="n">
         <v>6</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H129" t="n">
+        <v>3</v>
+      </c>
+      <c r="I129" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="130">
@@ -5266,21 +6044,27 @@
       <c r="C130" t="n">
         <v>64</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
         <v>272.6</v>
       </c>
-      <c r="E130" t="n">
+      <c r="G130" t="n">
         <v>5</v>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H130" t="n">
+        <v>3</v>
+      </c>
+      <c r="I130" t="n">
+        <v>384</v>
       </c>
     </row>
     <row r="131">
@@ -5295,21 +6079,27 @@
       <c r="C131" t="n">
         <v>64</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
         <v>2</v>
       </c>
-      <c r="E131" t="n">
+      <c r="G131" t="n">
         <v>1</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="132">
@@ -5324,21 +6114,27 @@
       <c r="C132" t="n">
         <v>48</v>
       </c>
-      <c r="D132" t="n">
-        <v>124</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>5</v>
+      </c>
+      <c r="H132" t="n">
         <v>3</v>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I132" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="133">
@@ -5353,21 +6149,27 @@
       <c r="C133" t="n">
         <v>40</v>
       </c>
-      <c r="D133" t="n">
-        <v>177</v>
-      </c>
-      <c r="E133" t="n">
-        <v>5</v>
-      </c>
-      <c r="F133" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>270.2999999999997</v>
+      </c>
+      <c r="G133" t="n">
+        <v>7</v>
+      </c>
+      <c r="H133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I133" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="134">
@@ -5382,21 +6184,27 @@
       <c r="C134" t="n">
         <v>32</v>
       </c>
-      <c r="D134" t="n">
-        <v>175</v>
-      </c>
-      <c r="E134" t="n">
-        <v>6</v>
-      </c>
-      <c r="F134" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>8</v>
+      </c>
+      <c r="H134" t="n">
+        <v>4</v>
+      </c>
+      <c r="I134" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="135">
@@ -5411,21 +6219,27 @@
       <c r="C135" t="n">
         <v>40</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
         <v>110</v>
       </c>
-      <c r="E135" t="n">
+      <c r="G135" t="n">
         <v>3</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H135" t="n">
+        <v>2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="136">
@@ -5440,21 +6254,27 @@
       <c r="C136" t="n">
         <v>32</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
         <v>20.2</v>
       </c>
-      <c r="E136" t="n">
+      <c r="G136" t="n">
         <v>1</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="137">
@@ -5469,21 +6289,27 @@
       <c r="C137" t="n">
         <v>42</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
         <v>41</v>
       </c>
-      <c r="E137" t="n">
+      <c r="G137" t="n">
         <v>1</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="138">
@@ -5498,21 +6324,27 @@
       <c r="C138" t="n">
         <v>20</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
         <v>43.40000000000001</v>
       </c>
-      <c r="E138" t="n">
+      <c r="G138" t="n">
         <v>3</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H138" t="n">
+        <v>2</v>
+      </c>
+      <c r="I138" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="139">
@@ -5527,21 +6359,27 @@
       <c r="C139" t="n">
         <v>133</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
         <v>107.4</v>
       </c>
-      <c r="E139" t="n">
+      <c r="G139" t="n">
         <v>1</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>266</v>
       </c>
     </row>
     <row r="140">
@@ -5556,21 +6394,27 @@
       <c r="C140" t="n">
         <v>48</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
         <v>54.80000000000001</v>
       </c>
-      <c r="E140" t="n">
+      <c r="G140" t="n">
         <v>2</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="141">
@@ -5585,21 +6429,27 @@
       <c r="C141" t="n">
         <v>32</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
         <v>45.80000000000001</v>
       </c>
-      <c r="E141" t="n">
+      <c r="G141" t="n">
         <v>2</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="142">
@@ -5614,21 +6464,27 @@
       <c r="C142" t="n">
         <v>60</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
         <v>45.40000000000003</v>
       </c>
-      <c r="E142" t="n">
+      <c r="G142" t="n">
         <v>1</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="143">
@@ -5643,21 +6499,27 @@
       <c r="C143" t="n">
         <v>32</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
         <v>37</v>
       </c>
-      <c r="E143" t="n">
+      <c r="G143" t="n">
         <v>2</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="144">
@@ -5672,21 +6534,27 @@
       <c r="C144" t="n">
         <v>20</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
         <v>162.4</v>
       </c>
-      <c r="E144" t="n">
+      <c r="G144" t="n">
         <v>9</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H144" t="n">
+        <v>5</v>
+      </c>
+      <c r="I144" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="145">
@@ -5701,21 +6569,27 @@
       <c r="C145" t="n">
         <v>35</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
         <v>118.9</v>
       </c>
-      <c r="E145" t="n">
+      <c r="G145" t="n">
         <v>4</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H145" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="146">
@@ -5730,21 +6604,27 @@
       <c r="C146" t="n">
         <v>60</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
         <v>91.60000000000002</v>
       </c>
-      <c r="E146" t="n">
+      <c r="G146" t="n">
         <v>2</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="147">
@@ -5759,21 +6639,27 @@
       <c r="C147" t="n">
         <v>60</v>
       </c>
-      <c r="D147" t="n">
-        <v>360.8000000000001</v>
-      </c>
-      <c r="E147" t="n">
-        <v>7</v>
-      </c>
-      <c r="F147" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>669.01</v>
+      </c>
+      <c r="G147" t="n">
+        <v>12</v>
+      </c>
+      <c r="H147" t="n">
+        <v>6</v>
+      </c>
+      <c r="I147" t="n">
+        <v>720</v>
       </c>
     </row>
     <row r="148">
@@ -5788,21 +6674,27 @@
       <c r="C148" t="n">
         <v>32</v>
       </c>
-      <c r="D148" t="n">
-        <v>47.20000000000005</v>
-      </c>
-      <c r="E148" t="n">
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>94.18999999999983</v>
+      </c>
+      <c r="G148" t="n">
+        <v>3</v>
+      </c>
+      <c r="H148" t="n">
         <v>2</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I148" t="n">
+        <v>128</v>
       </c>
     </row>
     <row r="149">
@@ -5817,21 +6709,27 @@
       <c r="C149" t="n">
         <v>40</v>
       </c>
-      <c r="D149" t="n">
-        <v>45</v>
-      </c>
-      <c r="E149" t="n">
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>92.1875</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3</v>
+      </c>
+      <c r="H149" t="n">
         <v>2</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I149" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="150">
@@ -5846,21 +6744,27 @@
       <c r="C150" t="n">
         <v>20</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
         <v>15.09999999999999</v>
       </c>
-      <c r="E150" t="n">
+      <c r="G150" t="n">
         <v>1</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="151">
@@ -5875,21 +6779,27 @@
       <c r="C151" t="n">
         <v>20</v>
       </c>
-      <c r="D151" t="n">
-        <v>27</v>
-      </c>
-      <c r="E151" t="n">
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>61.65000000000009</v>
+      </c>
+      <c r="G151" t="n">
+        <v>4</v>
+      </c>
+      <c r="H151" t="n">
         <v>2</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I151" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="152">
@@ -5904,21 +6814,27 @@
       <c r="C152" t="n">
         <v>112</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
         <v>107.6</v>
       </c>
-      <c r="E152" t="n">
+      <c r="G152" t="n">
         <v>1</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="153">
@@ -5933,21 +6849,27 @@
       <c r="C153" t="n">
         <v>20</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
         <v>115.8</v>
       </c>
-      <c r="E153" t="n">
+      <c r="G153" t="n">
         <v>6</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H153" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="154">
@@ -5962,21 +6884,27 @@
       <c r="C154" t="n">
         <v>60</v>
       </c>
-      <c r="D154" t="n">
-        <v>414</v>
-      </c>
-      <c r="E154" t="n">
-        <v>7</v>
-      </c>
-      <c r="F154" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>918.2500000000011</v>
+      </c>
+      <c r="G154" t="n">
+        <v>16</v>
+      </c>
+      <c r="H154" t="n">
+        <v>8</v>
+      </c>
+      <c r="I154" t="n">
+        <v>960</v>
       </c>
     </row>
     <row r="155">
@@ -5991,21 +6919,27 @@
       <c r="C155" t="n">
         <v>40</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
         <v>1.9</v>
       </c>
-      <c r="E155" t="n">
+      <c r="G155" t="n">
         <v>1</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="156">
@@ -6020,21 +6954,27 @@
       <c r="C156" t="n">
         <v>64</v>
       </c>
-      <c r="D156" t="n">
-        <v>70.40000000000003</v>
-      </c>
-      <c r="E156" t="n">
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>174.3999999999997</v>
+      </c>
+      <c r="G156" t="n">
+        <v>3</v>
+      </c>
+      <c r="H156" t="n">
         <v>2</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I156" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="157">
@@ -6049,21 +6989,27 @@
       <c r="C157" t="n">
         <v>36</v>
       </c>
-      <c r="D157" t="n">
-        <v>75.90000000000003</v>
-      </c>
-      <c r="E157" t="n">
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>200.5199999999993</v>
+      </c>
+      <c r="G157" t="n">
+        <v>6</v>
+      </c>
+      <c r="H157" t="n">
         <v>3</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I157" t="n">
+        <v>216</v>
       </c>
     </row>
     <row r="158">
@@ -6078,21 +7024,27 @@
       <c r="C158" t="n">
         <v>60</v>
       </c>
-      <c r="D158" t="n">
-        <v>129</v>
-      </c>
-      <c r="E158" t="n">
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>302.9500000000014</v>
+      </c>
+      <c r="G158" t="n">
+        <v>6</v>
+      </c>
+      <c r="H158" t="n">
         <v>3</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I158" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="159">
@@ -6107,21 +7059,27 @@
       <c r="C159" t="n">
         <v>20</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
         <v>81</v>
       </c>
-      <c r="E159" t="n">
+      <c r="G159" t="n">
         <v>5</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H159" t="n">
+        <v>3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="160">
@@ -6136,21 +7094,27 @@
       <c r="C160" t="n">
         <v>48</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
         <v>52.40000000000001</v>
       </c>
-      <c r="E160" t="n">
+      <c r="G160" t="n">
         <v>2</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="161">
@@ -6165,21 +7129,27 @@
       <c r="C161" t="n">
         <v>20</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
         <v>34</v>
       </c>
-      <c r="E161" t="n">
+      <c r="G161" t="n">
         <v>2</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="162">
@@ -6194,21 +7164,27 @@
       <c r="C162" t="n">
         <v>40</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
         <v>2.52778</v>
       </c>
-      <c r="E162" t="n">
+      <c r="G162" t="n">
         <v>1</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="163">
@@ -6223,21 +7199,27 @@
       <c r="C163" t="n">
         <v>20</v>
       </c>
-      <c r="D163" t="n">
-        <v>143</v>
-      </c>
-      <c r="E163" t="n">
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>305</v>
+      </c>
+      <c r="G163" t="n">
+        <v>16</v>
+      </c>
+      <c r="H163" t="n">
         <v>8</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I163" t="n">
+        <v>320</v>
       </c>
     </row>
     <row r="164">
@@ -6252,21 +7234,27 @@
       <c r="C164" t="n">
         <v>72</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
         <v>70</v>
       </c>
-      <c r="E164" t="n">
+      <c r="G164" t="n">
         <v>1</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="165">
@@ -6281,21 +7269,27 @@
       <c r="C165" t="n">
         <v>64</v>
       </c>
-      <c r="D165" t="n">
-        <v>335.2</v>
-      </c>
-      <c r="E165" t="n">
-        <v>6</v>
-      </c>
-      <c r="F165" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>600.3199999999974</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="n">
+        <v>5</v>
+      </c>
+      <c r="I165" t="n">
+        <v>640</v>
       </c>
     </row>
     <row r="166">
@@ -6310,21 +7304,27 @@
       <c r="C166" t="n">
         <v>48</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
         <v>32.20000000000002</v>
       </c>
-      <c r="E166" t="n">
+      <c r="G166" t="n">
         <v>1</v>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="167">
@@ -6339,21 +7339,27 @@
       <c r="C167" t="n">
         <v>72</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
         <v>39</v>
       </c>
-      <c r="E167" t="n">
+      <c r="G167" t="n">
         <v>1</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="168">
@@ -6368,21 +7374,27 @@
       <c r="C168" t="n">
         <v>40</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
         <v>14</v>
       </c>
-      <c r="E168" t="n">
+      <c r="G168" t="n">
         <v>1</v>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H168" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="169">
@@ -6397,21 +7409,27 @@
       <c r="C169" t="n">
         <v>64</v>
       </c>
-      <c r="D169" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="E169" t="n">
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>405.9500000000001</v>
+      </c>
+      <c r="G169" t="n">
+        <v>7</v>
+      </c>
+      <c r="H169" t="n">
         <v>4</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I169" t="n">
+        <v>512</v>
       </c>
     </row>
     <row r="170">
@@ -6426,21 +7444,27 @@
       <c r="C170" t="n">
         <v>72</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
         <v>35</v>
       </c>
-      <c r="E170" t="n">
+      <c r="G170" t="n">
         <v>1</v>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="171">
@@ -6455,21 +7479,27 @@
       <c r="C171" t="n">
         <v>30</v>
       </c>
-      <c r="D171" t="n">
-        <v>293.3</v>
-      </c>
-      <c r="E171" t="n">
-        <v>10</v>
-      </c>
-      <c r="F171" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>633.0699999999995</v>
+      </c>
+      <c r="G171" t="n">
+        <v>22</v>
+      </c>
+      <c r="H171" t="n">
+        <v>11</v>
+      </c>
+      <c r="I171" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="172">
@@ -6484,21 +7514,27 @@
       <c r="C172" t="n">
         <v>112</v>
       </c>
-      <c r="D172" t="n">
-        <v>98.49999999999994</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>260.2700000000001</v>
+      </c>
+      <c r="G172" t="n">
+        <v>3</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2</v>
+      </c>
+      <c r="I172" t="n">
+        <v>448</v>
       </c>
     </row>
     <row r="173">
@@ -6513,21 +7549,27 @@
       <c r="C173" t="n">
         <v>72</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
         <v>114.2</v>
       </c>
-      <c r="E173" t="n">
+      <c r="G173" t="n">
         <v>2</v>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="174">
@@ -6542,21 +7584,27 @@
       <c r="C174" t="n">
         <v>42</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
         <v>41</v>
       </c>
-      <c r="E174" t="n">
+      <c r="G174" t="n">
         <v>1</v>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H174" t="n">
+        <v>1</v>
+      </c>
+      <c r="I174" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="175">
@@ -6571,21 +7619,27 @@
       <c r="C175" t="n">
         <v>48</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
         <v>61.8</v>
       </c>
-      <c r="E175" t="n">
+      <c r="G175" t="n">
         <v>2</v>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="176">
@@ -6600,21 +7654,27 @@
       <c r="C176" t="n">
         <v>20</v>
       </c>
-      <c r="D176" t="n">
-        <v>63.20000000000005</v>
-      </c>
-      <c r="E176" t="n">
-        <v>4</v>
-      </c>
-      <c r="F176" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>118.65</v>
+      </c>
+      <c r="G176" t="n">
+        <v>6</v>
+      </c>
+      <c r="H176" t="n">
+        <v>3</v>
+      </c>
+      <c r="I176" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="177">
@@ -6629,21 +7689,27 @@
       <c r="C177" t="n">
         <v>48</v>
       </c>
-      <c r="D177" t="n">
-        <v>246.6</v>
-      </c>
-      <c r="E177" t="n">
-        <v>6</v>
-      </c>
-      <c r="F177" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>473.92</v>
+      </c>
+      <c r="G177" t="n">
+        <v>10</v>
+      </c>
+      <c r="H177" t="n">
+        <v>5</v>
+      </c>
+      <c r="I177" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="178">
@@ -6658,21 +7724,27 @@
       <c r="C178" t="n">
         <v>20</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
         <v>39</v>
       </c>
-      <c r="E178" t="n">
+      <c r="G178" t="n">
         <v>2</v>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="179">
@@ -6687,21 +7759,27 @@
       <c r="C179" t="n">
         <v>30</v>
       </c>
-      <c r="D179" t="n">
-        <v>237.9</v>
-      </c>
-      <c r="E179" t="n">
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>448.5699999999994</v>
+      </c>
+      <c r="G179" t="n">
+        <v>15</v>
+      </c>
+      <c r="H179" t="n">
         <v>8</v>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I179" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="180">
@@ -6716,21 +7794,27 @@
       <c r="C180" t="n">
         <v>50</v>
       </c>
-      <c r="D180" t="n">
-        <v>109</v>
-      </c>
-      <c r="E180" t="n">
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>273.3999999999999</v>
+      </c>
+      <c r="G180" t="n">
+        <v>6</v>
+      </c>
+      <c r="H180" t="n">
         <v>3</v>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I180" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="181">
@@ -6745,21 +7829,27 @@
       <c r="C181" t="n">
         <v>60</v>
       </c>
-      <c r="D181" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>321.8700000000009</v>
+      </c>
+      <c r="G181" t="n">
+        <v>6</v>
+      </c>
+      <c r="H181" t="n">
+        <v>3</v>
+      </c>
+      <c r="I181" t="n">
+        <v>360</v>
       </c>
     </row>
     <row r="182">
@@ -6774,21 +7864,27 @@
       <c r="C182" t="n">
         <v>50</v>
       </c>
-      <c r="D182" t="n">
-        <v>181</v>
-      </c>
-      <c r="E182" t="n">
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>330.0800000000004</v>
+      </c>
+      <c r="G182" t="n">
+        <v>7</v>
+      </c>
+      <c r="H182" t="n">
         <v>4</v>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I182" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="183">
@@ -6803,21 +7899,27 @@
       <c r="C183" t="n">
         <v>50</v>
       </c>
-      <c r="D183" t="n">
-        <v>240.2</v>
-      </c>
-      <c r="E183" t="n">
-        <v>5</v>
-      </c>
-      <c r="F183" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>581.4600000000015</v>
+      </c>
+      <c r="G183" t="n">
+        <v>12</v>
+      </c>
+      <c r="H183" t="n">
+        <v>6</v>
+      </c>
+      <c r="I183" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="184">
@@ -6832,21 +7934,27 @@
       <c r="C184" t="n">
         <v>64</v>
       </c>
-      <c r="D184" t="n">
-        <v>351.3000000000001</v>
-      </c>
-      <c r="E184" t="n">
-        <v>6</v>
-      </c>
-      <c r="F184" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>881.8000000000004</v>
+      </c>
+      <c r="G184" t="n">
+        <v>14</v>
+      </c>
+      <c r="H184" t="n">
+        <v>7</v>
+      </c>
+      <c r="I184" t="n">
+        <v>896</v>
       </c>
     </row>
     <row r="185">
@@ -6861,21 +7969,27 @@
       <c r="C185" t="n">
         <v>64</v>
       </c>
-      <c r="D185" t="n">
-        <v>344.2000000000004</v>
-      </c>
-      <c r="E185" t="n">
-        <v>6</v>
-      </c>
-      <c r="F185" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>825.9599999999971</v>
+      </c>
+      <c r="G185" t="n">
+        <v>13</v>
+      </c>
+      <c r="H185" t="n">
+        <v>7</v>
+      </c>
+      <c r="I185" t="n">
+        <v>896</v>
       </c>
     </row>
     <row r="186">
@@ -6890,21 +8004,27 @@
       <c r="C186" t="n">
         <v>64</v>
       </c>
-      <c r="D186" t="n">
-        <v>505.4000000000001</v>
-      </c>
-      <c r="E186" t="n">
-        <v>8</v>
-      </c>
-      <c r="F186" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>1109.52</v>
+      </c>
+      <c r="G186" t="n">
+        <v>18</v>
+      </c>
+      <c r="H186" t="n">
+        <v>9</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1152</v>
       </c>
     </row>
     <row r="187">
@@ -6919,21 +8039,27 @@
       <c r="C187" t="n">
         <v>133</v>
       </c>
-      <c r="D187" t="n">
-        <v>385</v>
-      </c>
-      <c r="E187" t="n">
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>601.3600000000006</v>
+      </c>
+      <c r="G187" t="n">
+        <v>5</v>
+      </c>
+      <c r="H187" t="n">
         <v>3</v>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I187" t="n">
+        <v>798</v>
       </c>
     </row>
     <row r="188">
@@ -6948,21 +8074,27 @@
       <c r="C188" t="n">
         <v>133</v>
       </c>
-      <c r="D188" t="n">
-        <v>494.8000000000002</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>961.9299999999996</v>
+      </c>
+      <c r="G188" t="n">
+        <v>8</v>
+      </c>
+      <c r="H188" t="n">
         <v>4</v>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="I188" t="n">
+        <v>1064</v>
       </c>
     </row>
     <row r="189">
@@ -6977,21 +8109,27 @@
       <c r="C189" t="n">
         <v>133</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
         <v>386.9</v>
       </c>
-      <c r="E189" t="n">
+      <c r="G189" t="n">
         <v>3</v>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+      <c r="I189" t="n">
+        <v>532</v>
       </c>
     </row>
     <row r="190">
@@ -7006,21 +8144,27 @@
       <c r="C190" t="n">
         <v>112</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
         <v>1.41667</v>
       </c>
-      <c r="E190" t="n">
+      <c r="G190" t="n">
         <v>1</v>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H190" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="191">
@@ -7035,21 +8179,27 @@
       <c r="C191" t="n">
         <v>112</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
         <v>2.75</v>
       </c>
-      <c r="E191" t="n">
+      <c r="G191" t="n">
         <v>1</v>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H191" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="192">
@@ -7064,21 +8214,27 @@
       <c r="C192" t="n">
         <v>40</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
         <v>0.41666</v>
       </c>
-      <c r="E192" t="n">
+      <c r="G192" t="n">
         <v>1</v>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H192" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="193">
@@ -7093,21 +8249,27 @@
       <c r="C193" t="n">
         <v>32</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
         <v>61.20000000000006</v>
       </c>
-      <c r="E193" t="n">
+      <c r="G193" t="n">
         <v>2</v>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
+      <c r="H193" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="194">
@@ -7122,21 +8284,27 @@
       <c r="C194" t="n">
         <v>40</v>
       </c>
-      <c r="D194" t="n">
-        <v>80.20000000000005</v>
-      </c>
-      <c r="E194" t="n">
-        <v>3</v>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>157.6799999999998</v>
+      </c>
+      <c r="G194" t="n">
+        <v>4</v>
+      </c>
+      <c r="H194" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" t="n">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
